--- a/TemplateRankings/Rankings/results/Rankings - llm.xlsx
+++ b/TemplateRankings/Rankings/results/Rankings - llm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allis\OneDrive\Desktop\TemplateRankings\Rankings\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50664C23-8B4C-49EC-A856-C92DFA8925E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34032986-34A6-4AA7-B1D9-F241104A362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-3510" windowWidth="38620" windowHeight="21100" xr2:uid="{C464C8E2-BA16-4143-86DF-5FCF38022D0F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="100">
   <si>
     <t>Total Locations</t>
   </si>
@@ -335,9 +335,6 @@
     <t>teaches.~teaches</t>
   </si>
   <si>
-    <t>c.grades.Grade</t>
-  </si>
-  <si>
     <t>Completions</t>
   </si>
   <si>
@@ -519,6 +516,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -535,9 +535,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -884,7 +881,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -1182,7 +1179,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1294,11 +1291,11 @@
       </c>
       <c r="B17" s="4">
         <f>'formula - syn - len alpha'!U2</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4">
         <f>'formula - syn - len alpha'!V2</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4">
         <f>'formula - syn - len alpha'!Q2</f>
@@ -1306,11 +1303,11 @@
       </c>
       <c r="E17" s="4">
         <f>'formula - syn - len alpha'!R2</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F17" s="4">
         <f>'formula - syn - len alpha'!S2</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17" s="4">
         <f>'formula - syn - len alpha'!N2</f>
@@ -1318,11 +1315,11 @@
       </c>
       <c r="H17" s="4">
         <f>'formula - syn - len alpha'!O2</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17" s="4">
         <f>'formula - syn - len alpha'!P2</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J17" s="4">
         <f>'formula - syn - len alpha'!K2</f>
@@ -1330,11 +1327,11 @@
       </c>
       <c r="K17" s="4">
         <f>'formula - syn - len alpha'!L2</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L17" s="4">
         <f>'formula - syn - len alpha'!M2</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
@@ -1366,9 +1363,9 @@
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -1437,11 +1434,11 @@
       </c>
       <c r="B22" s="1">
         <f>'formula - first - len - alpha'!U2</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1">
         <f>'formula - first - len - alpha'!V2</f>
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D22" s="1">
         <f>'formula - first - len - alpha'!Q2</f>
@@ -1449,23 +1446,23 @@
       </c>
       <c r="E22" s="1">
         <f>'formula - first - len - alpha'!R2</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F22" s="1">
         <f>'formula - first - len - alpha'!S2</f>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G22" s="1">
         <f>'formula - first - len - alpha'!N2</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="1">
         <f>'formula - first - len - alpha'!O2</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I22" s="1">
         <f>'formula - first - len - alpha'!P2</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J22" s="1">
         <f>'formula - first - len - alpha'!K2</f>
@@ -1473,11 +1470,11 @@
       </c>
       <c r="K22" s="1">
         <f>'formula - first - len - alpha'!L2</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L22" s="1">
         <f>'formula - first - len - alpha'!M2</f>
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
@@ -1487,10 +1484,10 @@
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="17" t="s">
@@ -1511,15 +1508,15 @@
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="19"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="17" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
@@ -1529,14 +1526,14 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="20"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="2" t="s">
         <v>3</v>
       </c>
@@ -1575,7 +1572,7 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1587,11 +1584,11 @@
       </c>
       <c r="D28" s="1">
         <f>E17</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E28" s="1">
         <f>F17</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F28" s="1">
         <f>D6</f>
@@ -1611,11 +1608,11 @@
       </c>
       <c r="J28" s="10">
         <f t="shared" ref="J28:N28" si="0">(D28/$I$24)*100</f>
-        <v>33.333333333333329</v>
+        <v>35.087719298245609</v>
       </c>
       <c r="K28" s="10">
         <f t="shared" si="0"/>
-        <v>58.771929824561411</v>
+        <v>60.526315789473685</v>
       </c>
       <c r="L28" s="10">
         <f t="shared" si="0"/>
@@ -1637,7 +1634,7 @@
       <c r="AC28" s="9"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="8" t="s">
         <v>6</v>
       </c>
@@ -1647,11 +1644,11 @@
       </c>
       <c r="D29" s="1">
         <f>B17</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1">
         <f>C17</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F29" s="1">
         <f>A6</f>
@@ -1671,11 +1668,11 @@
       </c>
       <c r="J29" s="10">
         <f t="shared" ref="J29:J33" si="2">(D29/$I$24)*100</f>
-        <v>51.754385964912288</v>
+        <v>52.631578947368418</v>
       </c>
       <c r="K29" s="10">
         <f t="shared" ref="K29:K33" si="3">(E29/$I$24)*100</f>
-        <v>77.192982456140342</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="L29" s="10">
         <f t="shared" ref="L29:L33" si="4">(F29/$I$24)*100</f>
@@ -1697,7 +1694,7 @@
       <c r="AC29" s="9"/>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="8" t="s">
         <v>17</v>
       </c>
@@ -1707,11 +1704,11 @@
       </c>
       <c r="D30" s="11">
         <f>K17</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E30" s="11">
         <f>L17</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F30" s="13">
         <f>J6</f>
@@ -1731,11 +1728,11 @@
       </c>
       <c r="J30" s="12">
         <f t="shared" si="2"/>
-        <v>73.68421052631578</v>
+        <v>76.31578947368422</v>
       </c>
       <c r="K30" s="12">
         <f t="shared" si="3"/>
-        <v>82.456140350877192</v>
+        <v>84.210526315789465</v>
       </c>
       <c r="L30" s="14">
         <f t="shared" si="4"/>
@@ -1769,11 +1766,11 @@
       </c>
       <c r="D31" s="13">
         <f>E22</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E31" s="13">
         <f>F22</f>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F31" s="13">
         <f>D11</f>
@@ -1793,11 +1790,11 @@
       </c>
       <c r="J31" s="14">
         <f t="shared" si="2"/>
-        <v>42.105263157894733</v>
+        <v>44.736842105263158</v>
       </c>
       <c r="K31" s="14">
         <f t="shared" si="3"/>
-        <v>64.035087719298247</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="L31" s="14">
         <f t="shared" si="4"/>
@@ -1829,11 +1826,11 @@
       </c>
       <c r="D32" s="13">
         <f>B22</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E32" s="13">
         <f>C22</f>
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F32" s="13">
         <f>A11</f>
@@ -1853,11 +1850,11 @@
       </c>
       <c r="J32" s="14">
         <f t="shared" si="2"/>
-        <v>53.508771929824562</v>
+        <v>55.26315789473685</v>
       </c>
       <c r="K32" s="14">
         <f t="shared" si="3"/>
-        <v>72.807017543859658</v>
+        <v>75.438596491228068</v>
       </c>
       <c r="L32" s="14">
         <f t="shared" si="4"/>
@@ -1889,11 +1886,11 @@
       </c>
       <c r="D33" s="11">
         <f>K22</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E33" s="11">
         <f>L22</f>
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F33" s="13">
         <f>J11</f>
@@ -1913,11 +1910,11 @@
       </c>
       <c r="J33" s="12">
         <f t="shared" si="2"/>
-        <v>82.456140350877192</v>
+        <v>84.210526315789465</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="3"/>
-        <v>86.842105263157904</v>
+        <v>88.596491228070178</v>
       </c>
       <c r="L33" s="14">
         <f t="shared" si="4"/>
@@ -1994,7 +1991,7 @@
       <c r="D40" s="10"/>
       <c r="E40" s="10">
         <f>(E30-E28/E28)*100</f>
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="F40" s="10">
         <f>(F30-F28/F28)*100</f>
@@ -2024,7 +2021,7 @@
       <c r="D41" s="10"/>
       <c r="E41" s="10">
         <f>(E33-E31)/E31*100</f>
-        <v>35.61643835616438</v>
+        <v>32.894736842105267</v>
       </c>
       <c r="F41" s="10">
         <f>(F33-F31)/F31*100</f>
@@ -2058,11 +2055,11 @@
       </c>
       <c r="D42" s="10">
         <f>(D30-D29)/D29*100</f>
-        <v>42.372881355932201</v>
+        <v>45</v>
       </c>
       <c r="E42" s="10">
         <f>(E30-E29)/E29*100</f>
-        <v>6.8181818181818175</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F42" s="10">
         <f>(F30-F29)/F29*100</f>
@@ -2094,11 +2091,11 @@
       </c>
       <c r="D43" s="10">
         <f>(D33-D32)/D32*100</f>
-        <v>54.098360655737707</v>
+        <v>52.380952380952387</v>
       </c>
       <c r="E43" s="10">
         <f>(E33-E32)/E32*100</f>
-        <v>19.277108433734941</v>
+        <v>17.441860465116278</v>
       </c>
       <c r="F43" s="10">
         <f>(F33-F32)/F32*100</f>
@@ -2156,7 +2153,7 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10">
         <f>(H28-E28)/E28*100</f>
-        <v>0</v>
+        <v>-2.8985507246376812</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2170,11 +2167,11 @@
       </c>
       <c r="D50" s="10">
         <f>(G29-D29)/D29*100</f>
-        <v>-27.118644067796609</v>
+        <v>-28.333333333333332</v>
       </c>
       <c r="E50" s="10">
         <f t="shared" ref="E50:E54" si="11">(H29-E29)/E29*100</f>
-        <v>-26.136363636363637</v>
+        <v>-27.777777777777779</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2190,11 +2187,11 @@
       </c>
       <c r="D51" s="10">
         <f>(G30-D30)/D30*100</f>
-        <v>-21.428571428571427</v>
+        <v>-24.137931034482758</v>
       </c>
       <c r="E51" s="10">
         <f t="shared" si="11"/>
-        <v>-25.531914893617021</v>
+        <v>-27.083333333333332</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2206,7 +2203,7 @@
       <c r="D52" s="10"/>
       <c r="E52" s="10">
         <f>(H31-E31)/E31*100</f>
-        <v>4.10958904109589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2222,11 +2219,11 @@
       </c>
       <c r="D53" s="10">
         <f>(G32-D32)/D32*100</f>
-        <v>-18.032786885245901</v>
+        <v>-20.634920634920633</v>
       </c>
       <c r="E53" s="10">
         <f t="shared" si="11"/>
-        <v>-9.6385542168674707</v>
+        <v>-12.790697674418606</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2240,15 +2237,46 @@
       </c>
       <c r="D54" s="10">
         <f>(G33-D33)/D33*100</f>
-        <v>-15.957446808510639</v>
+        <v>-17.708333333333336</v>
       </c>
       <c r="E54" s="10">
         <f t="shared" si="11"/>
-        <v>-20.202020202020201</v>
+        <v>-21.782178217821784</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G9:I9"/>
@@ -2258,37 +2286,6 @@
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2296,8 +2293,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA10FE78-7FBF-404A-8FD0-6D59269E7833}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2381,7 +2381,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="J2" s="9">
         <f>G2/I2*100</f>
-        <v>46.296296296296298</v>
+        <v>51.851851851851848</v>
       </c>
       <c r="L2" t="s">
         <v>80</v>
@@ -2445,17 +2445,17 @@
         <v>37</v>
       </c>
       <c r="G3" s="15">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="H3">
         <v>35</v>
       </c>
       <c r="I3" s="15">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="J3" s="9">
         <f t="shared" ref="J3:J4" si="1">G3/I3*100</f>
-        <v>85.730337078651687</v>
+        <v>85.703592814371248</v>
       </c>
       <c r="L3" t="s">
         <v>81</v>
@@ -2500,26 +2500,26 @@
         <v>58</v>
       </c>
       <c r="D4" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E4" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F4" s="15">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4" s="15">
-        <v>1668</v>
+        <v>1588</v>
       </c>
       <c r="H4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" s="15">
-        <v>2794</v>
+        <v>2680</v>
       </c>
       <c r="J4" s="9">
         <f t="shared" si="1"/>
-        <v>59.699355762347885</v>
+        <v>59.253731343283576</v>
       </c>
       <c r="L4" t="s">
         <v>83</v>
@@ -2556,120 +2556,120 @@
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5">
-        <f>SUM(B2:B4)</f>
+        <f t="shared" ref="B5:I5" si="2">SUM(B2:B4)</f>
         <v>101</v>
       </c>
       <c r="C5">
-        <f>SUM(C2:C4)</f>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="D5">
-        <f>SUM(D2:D4)</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="E5">
-        <f>SUM(E2:E4)</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="F5">
-        <f>SUM(F2:F4)</f>
-        <v>107</v>
+        <f t="shared" si="2"/>
+        <v>105</v>
       </c>
       <c r="G5">
-        <f>SUM(G2:G4)</f>
-        <v>3982</v>
+        <f t="shared" si="2"/>
+        <v>3906</v>
       </c>
       <c r="H5">
-        <f>SUM(H2:H4)</f>
-        <v>103</v>
+        <f t="shared" si="2"/>
+        <v>102</v>
       </c>
       <c r="I5">
-        <f>SUM(I2:I4)</f>
-        <v>5518</v>
+        <f t="shared" si="2"/>
+        <v>5406</v>
       </c>
       <c r="J5" s="9">
         <f>G5/I5*100</f>
-        <v>72.163827473722364</v>
+        <v>72.253052164261931</v>
       </c>
       <c r="M5">
-        <f>SUM(M2:M4)</f>
+        <f t="shared" ref="M5:T5" si="3">SUM(M2:M4)</f>
         <v>71</v>
       </c>
       <c r="N5">
-        <f>SUM(N2:N4)</f>
+        <f t="shared" si="3"/>
         <v>71</v>
       </c>
       <c r="O5">
-        <f>SUM(O2:O4)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P5">
-        <f>SUM(P2:P4)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="Q5">
-        <f>SUM(Q2:Q4)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="R5">
-        <f>SUM(R2:R4)</f>
+        <f t="shared" si="3"/>
         <v>651</v>
       </c>
       <c r="S5">
-        <f>SUM(S2:S4)</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="T5">
-        <f>SUM(T2:T4)</f>
+        <f t="shared" si="3"/>
         <v>1003</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" ref="U5" si="2">R5/T5*100</f>
+        <f t="shared" ref="U5" si="4">R5/T5*100</f>
         <v>64.905284147557325</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24" t="s">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18" t="s">
         <v>88</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="I8" s="6"/>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="18" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="7" t="s">
         <v>89</v>
       </c>
@@ -2679,7 +2679,7 @@
       <c r="E9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="7" t="s">
         <v>89</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="I9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="24"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F10" s="9">
         <f>J2</f>
-        <v>46.296296296296298</v>
+        <v>51.851851851851848</v>
       </c>
       <c r="G10">
         <f>M2</f>
@@ -2739,35 +2739,35 @@
         <v>38</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C12" si="3">B3</f>
+        <f t="shared" ref="C11:C12" si="5">B3</f>
         <v>34</v>
       </c>
       <c r="D11">
-        <f t="shared" ref="D11:D12" si="4">H3</f>
+        <f t="shared" ref="D11:D12" si="6">H3</f>
         <v>35</v>
       </c>
       <c r="E11">
-        <f t="shared" ref="E11:E12" si="5">F3</f>
+        <f t="shared" ref="E11:E12" si="7">F3</f>
         <v>37</v>
       </c>
       <c r="F11" s="9">
-        <f t="shared" ref="F11:F12" si="6">J3</f>
-        <v>85.730337078651687</v>
+        <f t="shared" ref="F11:F12" si="8">J3</f>
+        <v>85.703592814371248</v>
       </c>
       <c r="G11">
-        <f t="shared" ref="G11:G12" si="7">M3</f>
+        <f t="shared" ref="G11:G12" si="9">M3</f>
         <v>30</v>
       </c>
       <c r="H11">
-        <f t="shared" ref="H11:H12" si="8">S3</f>
+        <f t="shared" ref="H11:H12" si="10">S3</f>
         <v>35</v>
       </c>
       <c r="I11">
-        <f t="shared" ref="I11:I12" si="9">Q3</f>
+        <f t="shared" ref="I11:I12" si="11">Q3</f>
         <v>35</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" ref="J11:J12" si="10">U3</f>
+        <f t="shared" ref="J11:J12" si="12">U3</f>
         <v>70.515463917525778</v>
       </c>
     </row>
@@ -2779,35 +2779,35 @@
         <v>67</v>
       </c>
       <c r="C12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>58</v>
       </c>
       <c r="D12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="5"/>
-        <v>61</v>
-      </c>
       <c r="F12" s="9">
-        <f t="shared" si="6"/>
-        <v>59.699355762347885</v>
+        <f t="shared" si="8"/>
+        <v>59.253731343283576</v>
       </c>
       <c r="G12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>36</v>
       </c>
       <c r="H12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="I12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>65.418502202643168</v>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       </c>
       <c r="D13">
         <f>SUM(D10:D12)</f>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <f>SUM(E10:E12)</f>
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F13" s="9">
         <f>J5</f>
-        <v>72.163827473722364</v>
+        <v>72.253052164261931</v>
       </c>
       <c r="G13">
         <f>M5</f>
@@ -2847,6 +2847,16 @@
       <c r="J13" s="9">
         <f>U5</f>
         <v>64.905284147557325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f>(C13-G13)/C13*100</f>
+        <v>29.702970297029701</v>
+      </c>
+      <c r="E15">
+        <f>(D13-H13)/D13*100</f>
+        <v>21.568627450980394</v>
       </c>
     </row>
   </sheetData>
@@ -2997,7 +3007,7 @@
         <v>114</v>
       </c>
       <c r="C5" s="16">
-        <f t="shared" ref="C5:K5" si="4">SUM(C2:C4)</f>
+        <f t="shared" ref="C5:J5" si="4">SUM(C2:C4)</f>
         <v>5518</v>
       </c>
       <c r="D5" s="16">
@@ -5178,7 +5188,7 @@
         <v>4</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>100021</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -7592,7 +7602,7 @@
         <v>4</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>100021</v>
       </c>
       <c r="G80" t="b">
         <v>1</v>
@@ -7611,7 +7621,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B16E629-BE23-4927-A006-8DC0A1918F94}">
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
@@ -7716,11 +7726,11 @@
       </c>
       <c r="L2">
         <f>COUNTIF(B1:B1000,"&lt;=5")</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M2">
         <f>COUNTIF(B1:B1000,"&lt;=10")</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2">
         <f>COUNTIF(C1:C1000,"=1")</f>
@@ -7728,11 +7738,11 @@
       </c>
       <c r="O2">
         <f>COUNTIF(C1:C1000,"&lt;=5")</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P2">
         <f>COUNTIF(C1:C1000,"&lt;=10")</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(D1:D1000,"=1")</f>
@@ -7740,11 +7750,11 @@
       </c>
       <c r="R2">
         <f>COUNTIF(D1:D1000,"&lt;=5")</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S2">
         <f>COUNTIF(D1:D1000,"&lt;=10")</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T2">
         <f>COUNTIF(E1:E1000,"=1")</f>
@@ -7752,11 +7762,11 @@
       </c>
       <c r="U2">
         <f>COUNTIF(E1:E1000,"&lt;=5")</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V2">
         <f>COUNTIF(E1:E1000,"&lt;=10")</f>
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -7819,22 +7829,22 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -7848,22 +7858,22 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>200021</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -7877,22 +7887,22 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -7906,19 +7916,19 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -7935,22 +7945,22 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -7964,22 +7974,22 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -7993,22 +8003,22 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -8112,7 +8122,7 @@
         <v>34</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>66</v>
@@ -8124,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -8138,22 +8148,22 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -8167,22 +8177,22 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -8202,16 +8212,16 @@
         <v>1</v>
       </c>
       <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18">
         <v>7</v>
       </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
       <c r="E18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -8225,22 +8235,22 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -8254,22 +8264,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -8283,22 +8293,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -8312,22 +8322,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -8341,19 +8351,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8373,16 +8383,16 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
         <v>11</v>
-      </c>
-      <c r="E24">
-        <v>13</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -8399,22 +8409,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -8428,22 +8438,22 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -8457,22 +8467,22 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -8486,19 +8496,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -8515,22 +8525,22 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -8544,19 +8554,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8573,22 +8583,22 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -8602,22 +8612,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -8631,22 +8641,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -8660,22 +8670,22 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>300021</v>
+        <v>2</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -8689,22 +8699,22 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B35">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -8718,22 +8728,22 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>300021</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -8747,22 +8757,22 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>200021</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
@@ -8776,19 +8786,19 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -8805,22 +8815,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B39">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>210121</v>
+        <v>1</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
@@ -8834,22 +8844,22 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
@@ -8863,22 +8873,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>210121</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -8892,19 +8902,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -8921,22 +8931,22 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
@@ -8950,19 +8960,19 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -8979,19 +8989,19 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -9008,19 +9018,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -9037,22 +9047,22 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
@@ -9066,19 +9076,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -9095,19 +9105,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -9124,22 +9134,22 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E50">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
@@ -9159,13 +9169,13 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -9182,22 +9192,22 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
@@ -9217,7 +9227,7 @@
         <v>2</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53">
         <v>7</v>
@@ -9240,19 +9250,19 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E54">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -9269,22 +9279,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
@@ -9298,22 +9308,22 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F56">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G56" t="b">
         <v>1</v>
@@ -9327,22 +9337,22 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
@@ -9356,22 +9366,22 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D58">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G58" t="b">
         <v>1</v>
@@ -9391,7 +9401,7 @@
         <v>2</v>
       </c>
       <c r="C59">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -9400,7 +9410,7 @@
         <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
@@ -9472,19 +9482,19 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -9507,13 +9517,13 @@
         <v>2</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -9588,7 +9598,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -9597,10 +9607,10 @@
         <v>8</v>
       </c>
       <c r="D66">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -9617,19 +9627,19 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>13</v>
       </c>
       <c r="D67">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -9646,19 +9656,19 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E68">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -9675,22 +9685,22 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D69">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
@@ -9704,19 +9714,19 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -9733,22 +9743,22 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B71">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D71">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E71">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F71">
-        <v>310031</v>
+        <v>7</v>
       </c>
       <c r="G71" t="b">
         <v>1</v>
@@ -9762,22 +9772,22 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>210031</v>
+        <v>1</v>
       </c>
       <c r="G72" t="b">
         <v>1</v>
@@ -9791,22 +9801,22 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C73">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F73">
-        <v>7</v>
+        <v>310031</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
@@ -9820,22 +9830,22 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>210031</v>
       </c>
       <c r="G74" t="b">
         <v>1</v>
@@ -9849,22 +9859,22 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G75" t="b">
         <v>1</v>
@@ -9878,19 +9888,19 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -9907,22 +9917,22 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
@@ -9936,22 +9946,22 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B78">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G78" t="b">
         <v>1</v>
@@ -9965,22 +9975,22 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
@@ -9994,19 +10004,19 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B80">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F80">
         <v>200021</v>
@@ -10023,7 +10033,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -10032,13 +10042,13 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
@@ -10052,22 +10062,22 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>200021</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -10081,7 +10091,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -10090,7 +10100,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -10110,19 +10120,19 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -10139,16 +10149,16 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -10168,19 +10178,19 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -10197,22 +10207,22 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D87">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
@@ -10232,13 +10242,13 @@
         <v>2</v>
       </c>
       <c r="C88">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -10255,22 +10265,22 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E89">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
@@ -10284,19 +10294,19 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D90">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -10313,7 +10323,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -10322,10 +10332,10 @@
         <v>9</v>
       </c>
       <c r="D91">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E91">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -10342,7 +10352,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -10351,10 +10361,10 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -10371,22 +10381,22 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D93">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="E93">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="b">
         <v>1</v>
@@ -10400,16 +10410,16 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -10429,22 +10439,22 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>100021</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
@@ -10487,19 +10497,19 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -10516,19 +10526,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -10545,30 +10555,88 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>51</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>11</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99">
+        <v>12</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>4</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>48</v>
       </c>
-      <c r="B99">
-        <v>1</v>
-      </c>
-      <c r="C99">
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
         <v>14</v>
       </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-      <c r="G99" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" t="b">
-        <v>1</v>
-      </c>
-      <c r="I99" t="b">
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10579,7 +10647,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB8245B-ACAA-4CF6-BED5-F5528E637D34}">
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -10681,23 +10749,23 @@
       </c>
       <c r="L2">
         <f>COUNTIF(B1:B1000,"&lt;=5")</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M2">
         <f>COUNTIF(B1:B1000,"&lt;=10")</f>
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N2">
         <f>COUNTIF(C1:C1000,"=1")</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2">
         <f>COUNTIF(C1:C1000,"&lt;=5")</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P2">
         <f>COUNTIF(C1:C1000,"&lt;=10")</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q2">
         <f>COUNTIF(D1:D1000,"=1")</f>
@@ -10705,11 +10773,11 @@
       </c>
       <c r="R2">
         <f>COUNTIF(D1:D1000,"&lt;=5")</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S2">
         <f>COUNTIF(D1:D1000,"&lt;=10")</f>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="T2">
         <f>COUNTIF(E1:E1000,"=1")</f>
@@ -10717,11 +10785,11 @@
       </c>
       <c r="U2">
         <f>COUNTIF(E1:E1000,"&lt;=5")</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V2">
         <f>COUNTIF(E1:E1000,"&lt;=10")</f>
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -10784,22 +10852,22 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -10813,22 +10881,22 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>200021</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -10842,22 +10910,22 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -10871,19 +10939,19 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -10900,22 +10968,22 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -10929,28 +10997,28 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -10958,28 +11026,28 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -11103,28 +11171,28 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -11132,28 +11200,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -11167,16 +11235,16 @@
         <v>1</v>
       </c>
       <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18">
         <v>7</v>
       </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
       <c r="E18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -11190,28 +11258,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <v>8</v>
       </c>
-      <c r="D19">
-        <v>106</v>
-      </c>
       <c r="E19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -11219,22 +11287,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -11248,28 +11316,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -11277,22 +11345,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -11306,19 +11374,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -11338,16 +11406,16 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
         <v>11</v>
-      </c>
-      <c r="E24">
-        <v>13</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -11364,28 +11432,28 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -11393,22 +11461,22 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -11422,28 +11490,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -11451,19 +11519,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -11480,28 +11548,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -11509,19 +11577,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -11538,19 +11606,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -11567,22 +11635,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -11596,19 +11664,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -11625,28 +11693,28 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -11654,19 +11722,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>135</v>
+        <v>12</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -11683,28 +11751,28 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B36">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F36">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -11712,28 +11780,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -11741,22 +11809,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>200021</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -11770,19 +11838,19 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -11799,28 +11867,28 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -11828,22 +11896,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -11857,28 +11925,28 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -11886,19 +11954,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -11915,22 +11983,22 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -11944,19 +12012,19 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -11973,19 +12041,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -12020,10 +12088,10 @@
         <v>1</v>
       </c>
       <c r="G47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -12031,22 +12099,22 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
@@ -12060,28 +12128,28 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -12089,19 +12157,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -12118,22 +12186,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E51">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
@@ -12147,28 +12215,28 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -12176,22 +12244,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
@@ -12211,7 +12279,7 @@
         <v>1</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -12234,19 +12302,19 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E55">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -12263,19 +12331,19 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D56">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -12292,28 +12360,28 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
@@ -12321,28 +12389,28 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E58">
         <v>2</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
@@ -12350,28 +12418,28 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -12385,7 +12453,7 @@
         <v>2</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -12394,7 +12462,7 @@
         <v>2</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="b">
         <v>1</v>
@@ -12484,10 +12552,10 @@
         <v>1</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -12495,28 +12563,28 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
@@ -12582,16 +12650,16 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -12617,7 +12685,7 @@
         <v>1</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -12640,28 +12708,28 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="b">
         <v>1</v>
@@ -12669,28 +12737,28 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="b">
         <v>1</v>
@@ -12698,19 +12766,19 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -12727,28 +12795,28 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E72">
         <v>3</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="b">
         <v>1</v>
@@ -12756,28 +12824,28 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E73">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="b">
         <v>1</v>
@@ -12785,28 +12853,28 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74">
         <v>19</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="b">
         <v>1</v>
@@ -12814,28 +12882,28 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="b">
         <v>1</v>
@@ -12843,22 +12911,22 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
@@ -12872,19 +12940,19 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -12901,28 +12969,28 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="b">
         <v>1</v>
@@ -12930,22 +12998,22 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B79">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>200021</v>
+        <v>1</v>
       </c>
       <c r="G79" t="b">
         <v>1</v>
@@ -12959,28 +13027,28 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="b">
         <v>1</v>
@@ -12988,28 +13056,28 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
         <v>16</v>
       </c>
-      <c r="E81">
-        <v>14</v>
-      </c>
       <c r="F81">
-        <v>1</v>
+        <v>200021</v>
       </c>
       <c r="G81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="b">
         <v>1</v>
@@ -13017,7 +13085,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -13026,13 +13094,13 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -13046,28 +13114,28 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E83">
         <v>2</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>100021</v>
       </c>
       <c r="G83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="b">
         <v>1</v>
@@ -13075,7 +13143,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -13084,7 +13152,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -13104,19 +13172,19 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -13133,16 +13201,16 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -13162,28 +13230,28 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="b">
         <v>1</v>
@@ -13191,28 +13259,28 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D88">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="b">
         <v>1</v>
@@ -13220,28 +13288,28 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="b">
         <v>1</v>
@@ -13249,28 +13317,28 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
+        <v>39</v>
+      </c>
+      <c r="D90">
         <v>9</v>
       </c>
-      <c r="D90">
-        <v>7</v>
-      </c>
       <c r="E90">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="b">
         <v>1</v>
@@ -13278,19 +13346,19 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D91">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -13307,7 +13375,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -13316,10 +13384,10 @@
         <v>9</v>
       </c>
       <c r="D92">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E92">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -13336,7 +13404,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -13345,10 +13413,10 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -13365,22 +13433,22 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="E94">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
@@ -13394,16 +13462,16 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -13423,22 +13491,22 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>100021</v>
       </c>
       <c r="G96" t="b">
         <v>1</v>
@@ -13481,19 +13549,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E98">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -13510,19 +13578,19 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -13539,30 +13607,88 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>51</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>11</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100">
+        <v>12</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>3</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>48</v>
       </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100">
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
         <v>14</v>
       </c>
-      <c r="D100">
-        <v>1</v>
-      </c>
-      <c r="E100">
-        <v>1</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" t="b">
-        <v>1</v>
-      </c>
-      <c r="I100" t="b">
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102" t="b">
         <v>1</v>
       </c>
     </row>
